--- a/AirPassengers.xlsx
+++ b/AirPassengers.xlsx
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\23691A3305\PowerBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2EE507A-CD34-4DFD-BD76-F064296BBA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E4EE30-E97F-4C25-B11F-A2335D32F8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39BF5691-9768-49AD-B13F-3931BF3A4EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="AirPassengers" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1300,6 +1311,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB87EE3-47D0-4C87-A5D7-BCB1AF9214F5}">
   <dimension ref="A1:B145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
